--- a/cross_border/port_transit_results0512.xlsx
+++ b/cross_border/port_transit_results0512.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://connecthkuhk-my.sharepoint.com/personal/u3011514_connect_hku_hk/Documents/Documents/Code/balala/Practice/cross_border/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="11_08B526049E4A2ADFE54878D642947E3BA46D9E66" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A869D19D-8E63-2B4F-AD77-52A13A7C0DE3}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_08B519CC1C7726DEE54878D64295D6FEB5EB83F0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DFAE731-796C-1C47-B02F-6B2FF0F12356}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>ID</t>
   </si>
@@ -100,61 +100,40 @@
     <t>深圳湾口岸_distance(km)</t>
   </si>
   <si>
-    <t>深圳湾口岸_transfers</t>
-  </si>
-  <si>
     <t>皇岗口岸_time(min)</t>
   </si>
   <si>
     <t>皇岗口岸_distance(km)</t>
   </si>
   <si>
-    <t>皇岗口岸_transfers</t>
-  </si>
-  <si>
     <t>文锦渡口岸_time(min)</t>
   </si>
   <si>
     <t>文锦渡口岸_distance(km)</t>
   </si>
   <si>
-    <t>文锦渡口岸_transfers</t>
-  </si>
-  <si>
     <t>莲塘口岸_time(min)</t>
   </si>
   <si>
     <t>莲塘口岸_distance(km)</t>
   </si>
   <si>
-    <t>莲塘口岸_transfers</t>
-  </si>
-  <si>
     <t>罗湖口岸_time(min)</t>
   </si>
   <si>
     <t>罗湖口岸_distance(km)</t>
   </si>
   <si>
-    <t>罗湖口岸_transfers</t>
-  </si>
-  <si>
     <t>福田口岸_time(min)</t>
   </si>
   <si>
     <t>福田口岸_distance(km)</t>
   </si>
   <si>
-    <t>福田口岸_transfers</t>
-  </si>
-  <si>
     <t>香港西九龙_time(min)</t>
   </si>
   <si>
     <t>香港西九龙_distance(km)</t>
-  </si>
-  <si>
-    <t>香港西九龙_transfers</t>
   </si>
   <si>
     <t>nearest_port</t>
@@ -557,32 +536,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AU2"/>
+  <dimension ref="A1:AN2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="19" max="19" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="21.1640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="21.1640625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="19.1640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="19.1640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="21.1640625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="21.1640625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="19.1640625" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="19.1640625" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="19.1640625" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="19.1640625" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="21.1640625" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="24.1640625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="22.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47">
+    <row r="1" spans="1:40">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -703,29 +663,8 @@
       <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
     </row>
-    <row r="2" spans="1:47">
+    <row r="2" spans="1:40">
       <c r="A2">
         <v>2</v>
       </c>
@@ -745,7 +684,7 @@
         <v>4.08</v>
       </c>
       <c r="G2" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="H2">
         <v>46</v>
@@ -754,7 +693,7 @@
         <v>3</v>
       </c>
       <c r="J2" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -763,7 +702,7 @@
         <v>4</v>
       </c>
       <c r="M2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="N2">
         <v>1</v>
@@ -775,10 +714,10 @@
         <v>770</v>
       </c>
       <c r="Q2" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="S2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="T2">
         <v>22.300240253175598</v>
@@ -793,7 +732,7 @@
         <v>114.1755443</v>
       </c>
       <c r="X2" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="Y2">
         <v>87.28</v>
@@ -802,66 +741,45 @@
         <v>44.26</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>81.38</v>
       </c>
       <c r="AB2">
-        <v>81.38</v>
+        <v>39.9</v>
       </c>
       <c r="AC2">
-        <v>39.9</v>
+        <v>75.150000000000006</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>36.159999999999997</v>
       </c>
       <c r="AE2">
-        <v>75.150000000000006</v>
+        <v>85.77</v>
       </c>
       <c r="AF2">
-        <v>36.159999999999997</v>
+        <v>44.45</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>55.27</v>
       </c>
       <c r="AH2">
-        <v>85.77</v>
+        <v>34.57</v>
       </c>
       <c r="AI2">
-        <v>44.45</v>
+        <v>59.9</v>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>38.32</v>
       </c>
       <c r="AK2">
-        <v>55.27</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="AL2">
-        <v>34.57</v>
-      </c>
-      <c r="AM2">
-        <v>0</v>
+        <v>2.83</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>46</v>
       </c>
       <c r="AN2">
-        <v>59.9</v>
-      </c>
-      <c r="AO2">
-        <v>38.32</v>
-      </c>
-      <c r="AP2">
-        <v>0</v>
-      </c>
-      <c r="AQ2">
-        <v>18.899999999999999</v>
-      </c>
-      <c r="AR2">
-        <v>2.83</v>
-      </c>
-      <c r="AS2">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>53</v>
-      </c>
-      <c r="AU2">
         <v>18.899999999999999</v>
       </c>
     </row>
